--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Bergström, Suvi Bergström</t>
+          <t>Suvi Bergström, Stefan Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136345725</v>
       </c>
       <c r="B2" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136345725</v>
       </c>
       <c r="B2" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136345725</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136345725</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136345725</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36362-2025 artfynd.xlsx
+++ b/artfynd/A 36362-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136345725</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
